--- a/internal_doc/05.测试设计/元数据操作故障测试.xlsx
+++ b/internal_doc/05.测试设计/元数据操作故障测试.xlsx
@@ -21,10 +21,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="B12" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="C12" authorId="0">
+    <comment ref="C13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -83,7 +80,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>2</t>
+          <t>------------</t>
         </r>
         <r>
           <rPr>
@@ -93,7 +90,8 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>、创建失败，实际操作成功，没有返回应答？结果：</t>
+          <t xml:space="preserve">已补充检测点，所有创建成功都需要验证基本功能是否可用
+</t>
         </r>
         <r>
           <rPr>
@@ -102,7 +100,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>1</t>
+          <t>2</t>
         </r>
         <r>
           <rPr>
@@ -112,8 +110,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">、创建重复，表可用；
-</t>
+          <t>、创建失败，实际操作成功，没有返回应答？结果：</t>
         </r>
         <r>
           <rPr>
@@ -122,7 +119,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>3</t>
+          <t>1</t>
         </r>
         <r>
           <rPr>
@@ -132,22 +129,37 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>、创建失败，故障恢复后创建成功，功能可用</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A32" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
+          <t xml:space="preserve">、创建重复，表可用；
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>3</t>
+        </r>
+        <r>
+          <rPr>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>Author:</t>
+          <t xml:space="preserve">、创建失败，故障恢复后创建成功，功能可用
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>--------</t>
         </r>
         <r>
           <rPr>
@@ -157,51 +169,22 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">
-可以选随机值</t>
+          <t>已补充检测点</t>
         </r>
       </text>
     </comment>
-    <comment ref="B100" authorId="0">
+    <comment ref="A34" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-1</t>
-        </r>
-        <r>
-          <rPr>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>、</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>cl</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -211,16 +194,32 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>考虑数据节点？创建</t>
-        </r>
-        <r>
-          <rPr>
+          <t xml:space="preserve">
+可以选随机值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B110" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>cl</t>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1</t>
         </r>
         <r>
           <rPr>
@@ -230,7 +229,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>时数据主节点故障，恢复后</t>
+          <t>、</t>
         </r>
         <r>
           <rPr>
@@ -249,32 +248,16 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">可用
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B114" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
+          <t>考虑数据节点？创建</t>
+        </r>
+        <r>
+          <rPr>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-1</t>
+          <t>cl</t>
         </r>
         <r>
           <rPr>
@@ -284,7 +267,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>、</t>
+          <t>时数据主节点故障，恢复后</t>
         </r>
         <r>
           <rPr>
@@ -303,99 +286,8 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>考虑数据节点？创建</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>cl</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>时数据主节点故障，恢复后</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>cl</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
           <t xml:space="preserve">可用
 </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A126" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-1</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>、补充</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>umount</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>场景</t>
         </r>
       </text>
     </comment>
@@ -406,11 +298,39 @@
             <b/>
             <sz val="9"/>
             <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
             <rFont val="宋体"/>
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>Author:</t>
+          <t>、</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>cl</t>
         </r>
         <r>
           <rPr>
@@ -420,8 +340,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">
-测试点：</t>
+          <t>考虑数据节点？创建</t>
         </r>
         <r>
           <rPr>
@@ -430,7 +349,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>1</t>
+          <t>cl</t>
         </r>
         <r>
           <rPr>
@@ -440,8 +359,72 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">、连续主降备？编目节点和数据节点？
+          <t>时数据主节点故障，恢复后</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>cl</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">可用
 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B145" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+测试点：</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>1</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>、连续主降备？编目节点和数据节点？</t>
         </r>
       </text>
     </comment>
@@ -450,7 +433,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="116">
   <si>
     <t>测试场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -804,20 +787,139 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、普通拥塞
+    <t>取典型值，执行过程中随机取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>次数取值？随机值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>umount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可能出现两种结果，但是要保证结果一致：1、创建成功，验证cl基本功能，可插入数据验证；2、创建失败，实际操作成功，没有返回应答；故障恢复后再次创建重复，表可用；3、创建失败，故障恢复后再次创建cl成功，向cl插入数据正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、普通拥塞（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>选择拥塞时间每次测试随机取值，记录测试数值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）
 2、时间设置超过9s延迟</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>取典型值，执行过程中随机取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>次数取值？随机值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>umount</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连续主降备操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元数据操作过程中主节点故障，连续多次主降备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主节点故障后重新选主，新主节点故障后再次选主，查看主备节点数据完整一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>data主节点所在主机异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>data备节点所在主机异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建cl成功，故障恢复后向cl插入数据成功，查询data主备节点上数据完整一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主机连续异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机多次构造主机异常，故障恢复后主备节点数据一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点所在主机连续异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog备节点所在主机连续异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机多次构造主机异常，故障恢复后执行create/dropCL成功，cl可以正常读写数据，查看catalog主备节点数据一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连续异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点正常退出后再次异常退出，故障恢复过程中主机异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次故障恢复后，查看主备节点数据完整一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主节点所在盘umount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备节点所在盘umount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障恢复后，主备节点数据一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主节点网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>达到心跳超时时间重新选主；故障恢复后，主备节点数据一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备节点网络单通</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -825,7 +927,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -868,6 +970,21 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.499984740745262"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.499984740745262"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -907,7 +1024,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -915,6 +1032,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1277,16 +1398,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G155"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.375" customWidth="1"/>
     <col min="2" max="2" width="7.375" customWidth="1"/>
     <col min="3" max="3" width="11.875" customWidth="1"/>
     <col min="4" max="4" width="21.125" customWidth="1"/>
-    <col min="5" max="5" width="18.125" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="31.25" customWidth="1"/>
-    <col min="7" max="7" width="16.125" customWidth="1"/>
+    <col min="7" max="7" width="78.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
@@ -1316,179 +1437,183 @@
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="s">
+      <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F3" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="E3" t="s">
+    <row r="4" spans="1:7">
+      <c r="E4" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="C4" t="s">
+    <row r="5" spans="1:7">
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="E5" t="s">
+    <row r="6" spans="1:7">
+      <c r="E6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="C6" t="s">
+    <row r="7" spans="1:7">
+      <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="E7" t="s">
+    <row r="8" spans="1:7">
+      <c r="E8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="B8" t="s">
+    <row r="9" spans="1:7">
+      <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>15</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="E9" t="s">
+    <row r="10" spans="1:7">
+      <c r="E10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
-      <c r="C10" t="s">
+    <row r="11" spans="1:7">
+      <c r="C11" t="s">
         <v>16</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
-      <c r="E11" t="s">
+    <row r="12" spans="1:7">
+      <c r="E12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="B12" t="s">
+    <row r="13" spans="1:7" ht="40.5">
+      <c r="B13" t="s">
         <v>6</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>7</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" t="s">
         <v>81</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E13" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="E13" t="s">
+      <c r="G13" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="E14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
-      <c r="D14" t="s">
+    <row r="15" spans="1:7">
+      <c r="D15" t="s">
         <v>19</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
-      <c r="E15" t="s">
+    <row r="16" spans="1:7">
+      <c r="E16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
-      <c r="C16" t="s">
+    <row r="17" spans="1:7">
+      <c r="C17" t="s">
         <v>17</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
-      <c r="E17" t="s">
+    <row r="18" spans="1:7">
+      <c r="E18" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="2" t="s">
+    <row r="19" spans="1:7">
+      <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="B20" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C20" t="s">
         <v>9</v>
-      </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="E19" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" t="s">
-        <v>86</v>
-      </c>
-      <c r="G19" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="C20" t="s">
-        <v>12</v>
       </c>
       <c r="E20" t="s">
         <v>23</v>
+      </c>
+      <c r="F20" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="E21" t="s">
         <v>24</v>
       </c>
+      <c r="F21" t="s">
+        <v>86</v>
+      </c>
+      <c r="G21" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="22" spans="1:7">
       <c r="C22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E22" t="s">
         <v>23</v>
@@ -1500,11 +1625,8 @@
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="B24" t="s">
-        <v>14</v>
-      </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E24" t="s">
         <v>23</v>
@@ -1516,8 +1638,11 @@
       </c>
     </row>
     <row r="26" spans="1:7">
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
       <c r="C26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E26" t="s">
         <v>23</v>
@@ -1529,441 +1654,436 @@
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="B28" t="s">
-        <v>6</v>
-      </c>
       <c r="C28" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E28" t="s">
         <v>23</v>
-      </c>
-      <c r="F28" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="E29" t="s">
         <v>24</v>
       </c>
-      <c r="F29" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="30" spans="1:7">
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
       <c r="C30" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E30" t="s">
         <v>23</v>
+      </c>
+      <c r="F30" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="E31" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="40.5">
-      <c r="A32" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>88</v>
+      <c r="F31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="C32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="E33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" t="s">
+        <v>26</v>
+      </c>
+      <c r="F35" t="s">
+        <v>87</v>
+      </c>
+      <c r="G35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="E36" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
-      <c r="C34" t="s">
+    <row r="37" spans="1:7">
+      <c r="C37" t="s">
         <v>12</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E37" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
-      <c r="E35" t="s">
+    <row r="38" spans="1:7">
+      <c r="E38" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
-      <c r="C36" t="s">
+    <row r="39" spans="1:7">
+      <c r="C39" t="s">
         <v>13</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E39" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
-      <c r="E37" t="s">
+    <row r="40" spans="1:7">
+      <c r="E40" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
-      <c r="B38" t="s">
+    <row r="41" spans="1:7">
+      <c r="B41" t="s">
         <v>14</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C41" t="s">
         <v>15</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E41" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
-      <c r="E39" t="s">
+    <row r="42" spans="1:7">
+      <c r="E42" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
-      <c r="C40" t="s">
+    <row r="43" spans="1:7">
+      <c r="C43" t="s">
         <v>16</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E43" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
-      <c r="E41" t="s">
+    <row r="44" spans="1:7">
+      <c r="E44" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
-      <c r="B42" t="s">
+    <row r="45" spans="1:7">
+      <c r="B45" t="s">
         <v>6</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C45" t="s">
         <v>7</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E45" t="s">
         <v>26</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F45" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
-      <c r="E43" t="s">
+    <row r="46" spans="1:7">
+      <c r="E46" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
-      <c r="C44" t="s">
+    <row r="47" spans="1:7">
+      <c r="C47" t="s">
         <v>17</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E47" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
-      <c r="E45" t="s">
+    <row r="48" spans="1:7">
+      <c r="E48" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="2" t="s">
+    <row r="49" spans="1:7">
+      <c r="A49" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="B50" t="s">
         <v>40</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C50" t="s">
         <v>42</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D50" t="s">
         <v>41</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E50" t="s">
         <v>52</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="F50" t="s">
         <v>37</v>
       </c>
-      <c r="G46" s="2"/>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="E47" t="s">
-        <v>53</v>
-      </c>
-      <c r="F47" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G48" s="2"/>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="E49" t="s">
-        <v>49</v>
-      </c>
-      <c r="F49" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
     </row>
     <row r="51" spans="1:7">
       <c r="E51" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F51" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="B53" t="s">
+        <v>40</v>
+      </c>
+      <c r="C53" t="s">
+        <v>42</v>
+      </c>
+      <c r="D53" t="s">
+        <v>41</v>
+      </c>
+      <c r="E53" t="s">
+        <v>48</v>
+      </c>
+      <c r="F53" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
-      <c r="E52" t="s">
-        <v>56</v>
-      </c>
-      <c r="F52" t="s">
+    <row r="54" spans="1:7">
+      <c r="E54" t="s">
+        <v>49</v>
+      </c>
+      <c r="F54" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="C54" t="s">
-        <v>12</v>
-      </c>
-      <c r="E54" t="s">
-        <v>58</v>
-      </c>
-    </row>
     <row r="55" spans="1:7">
-      <c r="C55" t="s">
-        <v>13</v>
-      </c>
-      <c r="E55" t="s">
-        <v>59</v>
-      </c>
+      <c r="A55" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
     </row>
     <row r="56" spans="1:7">
       <c r="B56" t="s">
+        <v>40</v>
+      </c>
+      <c r="C56" t="s">
+        <v>42</v>
+      </c>
+      <c r="D56" t="s">
+        <v>41</v>
+      </c>
+      <c r="E56" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="E57" t="s">
+        <v>55</v>
+      </c>
+      <c r="F57" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="E58" t="s">
+        <v>56</v>
+      </c>
+      <c r="F58" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="C60" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="C61" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="B62" t="s">
         <v>14</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C62" t="s">
         <v>15</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E62" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
-      <c r="C57" t="s">
+    <row r="63" spans="1:7">
+      <c r="C63" t="s">
         <v>16</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E63" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
-      <c r="B58" t="s">
+    <row r="64" spans="1:7">
+      <c r="B64" t="s">
         <v>6</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C64" t="s">
         <v>7</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E64" t="s">
         <v>50</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F64" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
-      <c r="C59" t="s">
+    <row r="65" spans="1:7">
+      <c r="C65" t="s">
         <v>17</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E65" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="2" t="s">
+    <row r="66" spans="1:7">
+      <c r="A66" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="B67" t="s">
         <v>40</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C67" t="s">
         <v>42</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D67" t="s">
         <v>41</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E67" t="s">
         <v>61</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="F67" t="s">
         <v>37</v>
       </c>
-      <c r="G60" s="2"/>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="E61" t="s">
+    </row>
+    <row r="68" spans="1:7">
+      <c r="E68" t="s">
         <v>62</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F68" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
-      <c r="A62" s="2" t="s">
+    <row r="69" spans="1:7">
+      <c r="A69" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="B70" t="s">
         <v>8</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C70" t="s">
         <v>9</v>
-      </c>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G62" s="2"/>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="E63" t="s">
-        <v>64</v>
-      </c>
-      <c r="F63" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="C64" t="s">
-        <v>12</v>
-      </c>
-      <c r="E64" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="E65" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="C66" t="s">
-        <v>13</v>
-      </c>
-      <c r="E66" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="E67" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="B68" t="s">
-        <v>14</v>
-      </c>
-      <c r="C68" t="s">
-        <v>15</v>
-      </c>
-      <c r="E68" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="E69" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="C70" t="s">
-        <v>16</v>
       </c>
       <c r="E70" t="s">
         <v>63</v>
+      </c>
+      <c r="F70" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="E71" t="s">
         <v>64</v>
       </c>
+      <c r="F71" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="72" spans="1:7">
-      <c r="B72" t="s">
-        <v>6</v>
-      </c>
       <c r="C72" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E72" t="s">
         <v>63</v>
@@ -1976,7 +2096,7 @@
     </row>
     <row r="74" spans="1:7">
       <c r="C74" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E74" t="s">
         <v>63</v>
@@ -1988,217 +2108,216 @@
       </c>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G76" s="2"/>
+      <c r="B76" t="s">
+        <v>14</v>
+      </c>
+      <c r="C76" t="s">
+        <v>15</v>
+      </c>
+      <c r="E76" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="77" spans="1:7">
       <c r="E77" t="s">
-        <v>67</v>
-      </c>
-      <c r="F77" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="C78" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E78" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="E79" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="80" spans="1:7">
+      <c r="B80" t="s">
+        <v>6</v>
+      </c>
       <c r="C80" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E80" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="E81" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="82" spans="1:7">
-      <c r="B82" t="s">
-        <v>14</v>
-      </c>
       <c r="C82" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E82" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="E83" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="B85" t="s">
+        <v>8</v>
+      </c>
+      <c r="C85" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" t="s">
+        <v>66</v>
+      </c>
+      <c r="F85" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="E86" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="84" spans="1:7">
-      <c r="C84" t="s">
+      <c r="F86" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="C87" t="s">
+        <v>12</v>
+      </c>
+      <c r="E87" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="E88" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="C89" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="E90" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="B91" t="s">
+        <v>14</v>
+      </c>
+      <c r="C91" t="s">
+        <v>15</v>
+      </c>
+      <c r="E91" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="E92" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="C93" t="s">
         <v>16</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E93" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
-      <c r="E85" t="s">
+    <row r="94" spans="1:7">
+      <c r="E94" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
-      <c r="B86" t="s">
+    <row r="95" spans="1:7">
+      <c r="B95" t="s">
         <v>6</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C95" t="s">
         <v>7</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E95" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
-      <c r="E87" t="s">
+    <row r="96" spans="1:7">
+      <c r="E96" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
-      <c r="C88" t="s">
+    <row r="97" spans="1:7">
+      <c r="C97" t="s">
         <v>17</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E97" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
-      <c r="E89" t="s">
+    <row r="98" spans="1:7">
+      <c r="E98" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
-      <c r="A90" s="2" t="s">
+    <row r="99" spans="1:7">
+      <c r="A99" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G90" s="2"/>
-    </row>
-    <row r="91" spans="1:7">
-      <c r="E91" t="s">
-        <v>69</v>
-      </c>
-      <c r="F91" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
-      <c r="C92" t="s">
-        <v>12</v>
-      </c>
-      <c r="E92" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
-      <c r="E93" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
-      <c r="C94" t="s">
-        <v>13</v>
-      </c>
-      <c r="E94" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
-      <c r="E95" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
-      <c r="B96" t="s">
-        <v>14</v>
-      </c>
-      <c r="C96" t="s">
-        <v>15</v>
-      </c>
-      <c r="E96" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
-      <c r="E97" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
-      <c r="C98" t="s">
-        <v>16</v>
-      </c>
-      <c r="E98" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
-      <c r="E99" t="s">
-        <v>69</v>
-      </c>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
     </row>
     <row r="100" spans="1:7">
       <c r="B100" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C100" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E100" t="s">
         <v>68</v>
+      </c>
+      <c r="F100" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="E101" t="s">
         <v>69</v>
       </c>
+      <c r="F101" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="102" spans="1:7">
       <c r="C102" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E102" t="s">
         <v>68</v>
@@ -2210,184 +2329,149 @@
       </c>
     </row>
     <row r="104" spans="1:7">
-      <c r="A104" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G104" s="2"/>
+      <c r="C104" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="105" spans="1:7">
       <c r="E105" t="s">
-        <v>71</v>
-      </c>
-      <c r="F105" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
     </row>
     <row r="106" spans="1:7">
+      <c r="B106" t="s">
+        <v>14</v>
+      </c>
       <c r="C106" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E106" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="E107" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="C108" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E108" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="E109" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="B110" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C110" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E110" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="E111" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="112" spans="1:7">
-      <c r="C112" t="s">
-        <v>16</v>
-      </c>
-      <c r="E112" t="s">
-        <v>70</v>
+      <c r="E112" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="113" spans="1:7">
-      <c r="E113" t="s">
-        <v>71</v>
+      <c r="E113" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F113" s="6" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="114" spans="1:7">
-      <c r="B114" t="s">
-        <v>6</v>
-      </c>
       <c r="C114" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E114" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="E115" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
+      <c r="E116" s="2"/>
+      <c r="F116" s="2"/>
+      <c r="G116" s="2"/>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="B117" t="s">
+        <v>8</v>
+      </c>
+      <c r="C117" t="s">
+        <v>9</v>
+      </c>
+      <c r="E117" t="s">
+        <v>70</v>
+      </c>
+      <c r="F117" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="E118" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="116" spans="1:7">
-      <c r="C116" t="s">
-        <v>17</v>
-      </c>
-      <c r="E116" t="s">
+      <c r="F118" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="C119" t="s">
+        <v>12</v>
+      </c>
+      <c r="E119" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
-      <c r="E117" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
-      <c r="A118" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G118" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
-      <c r="E119" t="s">
-        <v>44</v>
-      </c>
-      <c r="F119" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="120" spans="1:7">
       <c r="E120" t="s">
-        <v>45</v>
-      </c>
-      <c r="F120" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
     </row>
     <row r="121" spans="1:7">
-      <c r="A121" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G121" s="3" t="s">
-        <v>90</v>
+      <c r="C121" t="s">
+        <v>13</v>
+      </c>
+      <c r="E121" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="E122" t="s">
-        <v>76</v>
-      </c>
-      <c r="F122" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -2395,55 +2479,353 @@
         <v>14</v>
       </c>
       <c r="C123" t="s">
-        <v>74</v>
-      </c>
-      <c r="D123" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="E123" t="s">
-        <v>72</v>
-      </c>
-      <c r="F123" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="E124" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="C125" t="s">
+        <v>16</v>
+      </c>
+      <c r="E125" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="E126" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="B127" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" t="s">
+        <v>7</v>
+      </c>
+      <c r="E127" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="E128" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="E129" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="E130" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F130" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="C131" t="s">
+        <v>17</v>
+      </c>
+      <c r="E131" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="E132" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B133" s="2"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2"/>
+      <c r="F133" s="2"/>
+      <c r="G133" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="B134" t="s">
+        <v>40</v>
+      </c>
+      <c r="C134" t="s">
+        <v>42</v>
+      </c>
+      <c r="D134" t="s">
+        <v>41</v>
+      </c>
+      <c r="E134" t="s">
+        <v>43</v>
+      </c>
+      <c r="F134" t="s">
+        <v>47</v>
+      </c>
+      <c r="G134" s="3"/>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="E135" t="s">
+        <v>44</v>
+      </c>
+      <c r="F135" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="E136" t="s">
+        <v>45</v>
+      </c>
+      <c r="F136" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B137" s="2"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2"/>
+      <c r="F137" s="2"/>
+      <c r="G137" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="B138" t="s">
+        <v>8</v>
+      </c>
+      <c r="C138" t="s">
+        <v>8</v>
+      </c>
+      <c r="D138" t="s">
+        <v>75</v>
+      </c>
+      <c r="E138" t="s">
+        <v>72</v>
+      </c>
+      <c r="F138" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="E139" t="s">
         <v>76</v>
       </c>
-      <c r="F124" t="s">
+      <c r="F139" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
-      <c r="B125" t="s">
+    <row r="140" spans="1:7">
+      <c r="B140" t="s">
+        <v>14</v>
+      </c>
+      <c r="C140" t="s">
+        <v>74</v>
+      </c>
+      <c r="D140" t="s">
+        <v>78</v>
+      </c>
+      <c r="E140" t="s">
+        <v>72</v>
+      </c>
+      <c r="F140" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="E141" t="s">
+        <v>76</v>
+      </c>
+      <c r="F141" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="B142" t="s">
         <v>79</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C142" t="s">
         <v>80</v>
       </c>
-      <c r="D125" t="s">
+      <c r="D142" t="s">
         <v>75</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E142" t="s">
         <v>72</v>
       </c>
-      <c r="F125" t="s">
+      <c r="F142" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
-      <c r="A126" t="s">
-        <v>91</v>
-      </c>
-      <c r="E126" t="s">
+    <row r="143" spans="1:7">
+      <c r="E143" t="s">
         <v>76</v>
       </c>
-      <c r="F126" t="s">
+      <c r="F143" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="127" spans="1:7"/>
+    <row r="144" spans="1:7">
+      <c r="B144" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E144" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F144" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="G144" s="6"/>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="B145" s="6"/>
+      <c r="C145" s="6"/>
+      <c r="D145" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F145" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="G145" s="6"/>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="B146" s="6"/>
+      <c r="C146" s="6"/>
+      <c r="D146" s="6"/>
+      <c r="E146" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F146" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G146" s="6"/>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="B147" s="6"/>
+      <c r="C147" s="6"/>
+      <c r="D147" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F147" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="G147" s="6"/>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="B148" s="6"/>
+      <c r="C148" s="6"/>
+      <c r="D148" s="6"/>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B149" s="2"/>
+      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
+      <c r="E149" s="2"/>
+      <c r="F149" s="2"/>
+      <c r="G149" s="2"/>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="B150" t="s">
+        <v>40</v>
+      </c>
+      <c r="C150" t="s">
+        <v>42</v>
+      </c>
+      <c r="D150" t="s">
+        <v>41</v>
+      </c>
+      <c r="E150" t="s">
+        <v>43</v>
+      </c>
+      <c r="F150" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="E151" t="s">
+        <v>109</v>
+      </c>
+      <c r="F151" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="E152" t="s">
+        <v>110</v>
+      </c>
+      <c r="F152" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="2"/>
+      <c r="F153" s="2"/>
+      <c r="G153" s="2"/>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="B154" t="s">
+        <v>40</v>
+      </c>
+      <c r="C154" t="s">
+        <v>42</v>
+      </c>
+      <c r="D154" t="s">
+        <v>41</v>
+      </c>
+      <c r="E154" t="s">
+        <v>113</v>
+      </c>
+      <c r="F154" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="E155" t="s">
+        <v>115</v>
+      </c>
+      <c r="F155" t="s">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
